--- a/artfynd/A 32396-2021 artfynd.xlsx
+++ b/artfynd/A 32396-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32396-2021 artfynd.xlsx
+++ b/artfynd/A 32396-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>90360174</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543809.383823512</v>
+        <v>543809</v>
       </c>
       <c r="R2" t="n">
-        <v>6399459.714013629</v>
+        <v>6399460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +783,7 @@
         <v>90360269</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543757.8591431272</v>
+        <v>543758</v>
       </c>
       <c r="R3" t="n">
-        <v>6399426.051616603</v>
+        <v>6399426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
